--- a/results/Risultati.xlsx
+++ b/results/Risultati.xlsx
@@ -5,7 +5,9 @@
   <sheets>
     <sheet state="visible" name="experiments-results-rust-python" sheetId="1" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'experiments-results-rust-python'!$A$1:$I$51</definedName>
+  </definedNames>
   <calcPr/>
 </workbook>
 </file>
@@ -1230,6 +1232,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.00000000"/>
+  </numFmts>
   <fonts count="5">
     <font>
       <sz val="10.0"/>
@@ -1256,18 +1261,12 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFF2CC"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1282,30 +1281,98 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="4" numFmtId="49" xfId="0" applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="5">
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="1">
+    <tableStyle count="4" pivot="0" name="experiments-results-rust-python-style">
+      <tableStyleElement dxfId="1" type="headerRow"/>
+      <tableStyleElement dxfId="2" type="firstRowStripe"/>
+      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+    </tableStyle>
+  </tableStyles>
 </styleSheet>
 </file>
 
@@ -1315,6 +1382,24 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:I51" displayName="Experiment_Results_Metrics" name="Experiment_Results_Metrics" id="1">
+  <autoFilter ref="$A$1:$I$51"/>
+  <tableColumns count="9">
+    <tableColumn name="dataset" id="1"/>
+    <tableColumn name="operating system" id="2"/>
+    <tableColumn name="target column" id="3"/>
+    <tableColumn name="reboot first execution time (seconds)" id="4"/>
+    <tableColumn name="common execution time (seconds)" id="5"/>
+    <tableColumn name="MCC" id="6"/>
+    <tableColumn name="energy consumption (kWh)" id="7"/>
+    <tableColumn name="energy consumption technology" id="8"/>
+    <tableColumn name="programming language and version" id="9"/>
+  </tableColumns>
+  <tableStyleInfo name="experiments-results-rust-python-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1518,17 +1603,17 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="12.63"/>
+    <col customWidth="1" min="1" max="1" width="28.0"/>
     <col customWidth="1" min="2" max="2" width="37.63"/>
     <col customWidth="1" min="3" max="3" width="17.25"/>
     <col customWidth="1" min="4" max="4" width="18.25"/>
-    <col customWidth="1" min="5" max="5" width="20.75"/>
+    <col customWidth="1" min="5" max="5" width="23.88"/>
     <col customWidth="1" min="6" max="6" width="19.5"/>
     <col customWidth="1" min="8" max="8" width="21.63"/>
     <col customWidth="1" min="9" max="9" width="22.5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
+    <row r="1" ht="48.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1575,19 +1660,19 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="4" t="s">
+      <c r="C2" s="3"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="5" t="s">
         <v>11</v>
       </c>
       <c r="J2" s="2"/>
@@ -1609,21 +1694,23 @@
       <c r="Z2" s="2"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="5" t="s">
+      <c r="C3" s="3"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="6">
+        <v>0.11894416809082</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="4" t="s">
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="5" t="s">
         <v>11</v>
       </c>
       <c r="J3" s="2"/>
@@ -1645,19 +1732,19 @@
       <c r="Z3" s="2"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="4" t="s">
+      <c r="C4" s="3"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="5" t="s">
         <v>11</v>
       </c>
       <c r="J4" s="2"/>
@@ -1679,19 +1766,19 @@
       <c r="Z4" s="2"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="4" t="s">
+      <c r="C5" s="3"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="5" t="s">
         <v>11</v>
       </c>
       <c r="J5" s="2"/>
@@ -1713,19 +1800,19 @@
       <c r="Z5" s="2"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="4" t="s">
+      <c r="C6" s="3"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="5" t="s">
         <v>11</v>
       </c>
       <c r="J6" s="2"/>
@@ -1747,19 +1834,19 @@
       <c r="Z6" s="2"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="4" t="s">
+      <c r="C7" s="3"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
+      <c r="I7" s="5" t="s">
         <v>11</v>
       </c>
       <c r="J7" s="2"/>
@@ -1781,19 +1868,19 @@
       <c r="Z7" s="2"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="4" t="s">
+      <c r="C8" s="3"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="5" t="s">
         <v>11</v>
       </c>
       <c r="J8" s="2"/>
@@ -1815,19 +1902,19 @@
       <c r="Z8" s="2"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="4" t="s">
+      <c r="C9" s="3"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="5" t="s">
         <v>11</v>
       </c>
       <c r="J9" s="2"/>
@@ -1849,19 +1936,19 @@
       <c r="Z9" s="2"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="4" t="s">
+      <c r="C10" s="3"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="5" t="s">
         <v>11</v>
       </c>
       <c r="J10" s="2"/>
@@ -1883,19 +1970,19 @@
       <c r="Z10" s="2"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="4" t="s">
+      <c r="C11" s="3"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="5" t="s">
         <v>11</v>
       </c>
       <c r="J11" s="2"/>
@@ -1917,19 +2004,19 @@
       <c r="Z11" s="2"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="4" t="s">
+      <c r="C12" s="3"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="5" t="s">
         <v>27</v>
       </c>
       <c r="J12" s="2"/>
@@ -1951,21 +2038,23 @@
       <c r="Z12" s="2"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="5" t="s">
+      <c r="C13" s="3"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="6">
+        <v>0.8567416809082</v>
+      </c>
+      <c r="F13" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="4" t="s">
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="5" t="s">
         <v>27</v>
       </c>
       <c r="J13" s="2"/>
@@ -1987,19 +2076,19 @@
       <c r="Z13" s="2"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="3" t="s">
         <v>15</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="4" t="s">
+      <c r="C14" s="3"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="5" t="s">
         <v>27</v>
       </c>
       <c r="J14" s="2"/>
@@ -2021,19 +2110,19 @@
       <c r="Z14" s="2"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="4" t="s">
+      <c r="C15" s="3"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="5" t="s">
         <v>27</v>
       </c>
       <c r="J15" s="2"/>
@@ -2055,19 +2144,19 @@
       <c r="Z15" s="2"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="4" t="s">
+      <c r="C16" s="3"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="5" t="s">
         <v>27</v>
       </c>
       <c r="J16" s="2"/>
@@ -2089,19 +2178,19 @@
       <c r="Z16" s="2"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="4" t="s">
+      <c r="C17" s="3"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="5" t="s">
         <v>27</v>
       </c>
       <c r="J17" s="2"/>
@@ -2123,19 +2212,19 @@
       <c r="Z17" s="2"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="B18" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="4" t="s">
+      <c r="C18" s="3"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="5" t="s">
         <v>27</v>
       </c>
       <c r="J18" s="2"/>
@@ -2157,19 +2246,19 @@
       <c r="Z18" s="2"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="4" t="s">
+      <c r="C19" s="3"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="5" t="s">
         <v>27</v>
       </c>
       <c r="J19" s="2"/>
@@ -2191,19 +2280,19 @@
       <c r="Z19" s="2"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="4" t="s">
+      <c r="C20" s="3"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="5" t="s">
         <v>27</v>
       </c>
       <c r="J20" s="2"/>
@@ -2225,19 +2314,19 @@
       <c r="Z20" s="2"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="4" t="s">
+      <c r="C21" s="3"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="5" t="s">
         <v>27</v>
       </c>
       <c r="J21" s="2"/>
@@ -2259,19 +2348,19 @@
       <c r="Z21" s="2"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="4" t="s">
+      <c r="C22" s="3"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="5" t="s">
         <v>39</v>
       </c>
       <c r="J22" s="2"/>
@@ -2293,21 +2382,23 @@
       <c r="Z22" s="2"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="5" t="s">
+      <c r="C23" s="3"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="6">
+        <v>0.002872</v>
+      </c>
+      <c r="F23" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="4" t="s">
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="5" t="s">
         <v>39</v>
       </c>
       <c r="J23" s="2"/>
@@ -2329,19 +2420,19 @@
       <c r="Z23" s="2"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="3" t="s">
         <v>15</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="4" t="s">
+      <c r="C24" s="3"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="5" t="s">
         <v>39</v>
       </c>
       <c r="J24" s="2"/>
@@ -2363,19 +2454,19 @@
       <c r="Z24" s="2"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="4" t="s">
+      <c r="C25" s="3"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="5" t="s">
         <v>39</v>
       </c>
       <c r="J25" s="2"/>
@@ -2397,19 +2488,19 @@
       <c r="Z25" s="2"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="4" t="s">
+      <c r="C26" s="3"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="5" t="s">
         <v>39</v>
       </c>
       <c r="J26" s="2"/>
@@ -2431,19 +2522,19 @@
       <c r="Z26" s="2"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B27" s="2" t="s">
+      <c r="B27" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="4" t="s">
+      <c r="C27" s="3"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="5" t="s">
         <v>39</v>
       </c>
       <c r="J27" s="2"/>
@@ -2465,19 +2556,19 @@
       <c r="Z27" s="2"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B28" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="4" t="s">
+      <c r="C28" s="3"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="5" t="s">
         <v>39</v>
       </c>
       <c r="J28" s="2"/>
@@ -2499,19 +2590,19 @@
       <c r="Z28" s="2"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B29" s="2" t="s">
+      <c r="B29" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="4" t="s">
+      <c r="C29" s="3"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="5" t="s">
         <v>39</v>
       </c>
       <c r="J29" s="2"/>
@@ -2533,19 +2624,19 @@
       <c r="Z29" s="2"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B30" s="2" t="s">
+      <c r="B30" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="4" t="s">
+      <c r="C30" s="3"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="5" t="s">
         <v>39</v>
       </c>
       <c r="J30" s="2"/>
@@ -2567,19 +2658,19 @@
       <c r="Z30" s="2"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="4" t="s">
+      <c r="C31" s="3"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="4"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="5" t="s">
         <v>39</v>
       </c>
       <c r="J31" s="2"/>
@@ -2601,19 +2692,19 @@
       <c r="Z31" s="2"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="4" t="s">
+      <c r="C32" s="3"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="5" t="s">
         <v>50</v>
       </c>
       <c r="J32" s="2"/>
@@ -2635,21 +2726,25 @@
       <c r="Z32" s="2"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="5" t="s">
+      <c r="C33" s="3"/>
+      <c r="D33" s="6">
+        <v>21.6710000038146</v>
+      </c>
+      <c r="E33" s="6">
+        <v>0.10099983215332</v>
+      </c>
+      <c r="F33" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="4" t="s">
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="5" t="s">
         <v>50</v>
       </c>
       <c r="J33" s="2"/>
@@ -2671,19 +2766,19 @@
       <c r="Z33" s="2"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="3" t="s">
         <v>15</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="4" t="s">
+      <c r="C34" s="3"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="5" t="s">
         <v>50</v>
       </c>
       <c r="J34" s="2"/>
@@ -2705,19 +2800,19 @@
       <c r="Z34" s="2"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-      <c r="E35" s="2"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-      <c r="I35" s="4" t="s">
+      <c r="C35" s="3"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="5" t="s">
         <v>50</v>
       </c>
       <c r="J35" s="2"/>
@@ -2739,19 +2834,19 @@
       <c r="Z35" s="2"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-      <c r="E36" s="2"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-      <c r="I36" s="4" t="s">
+      <c r="C36" s="3"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="5" t="s">
         <v>50</v>
       </c>
       <c r="J36" s="2"/>
@@ -2773,19 +2868,19 @@
       <c r="Z36" s="2"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B37" s="2" t="s">
+      <c r="B37" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="4" t="s">
+      <c r="C37" s="3"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="5" t="s">
         <v>50</v>
       </c>
       <c r="J37" s="2"/>
@@ -2807,19 +2902,19 @@
       <c r="Z37" s="2"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="2" t="s">
+      <c r="A38" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B38" s="2" t="s">
+      <c r="B38" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="4" t="s">
+      <c r="C38" s="3"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="5" t="s">
         <v>50</v>
       </c>
       <c r="J38" s="2"/>
@@ -2841,19 +2936,19 @@
       <c r="Z38" s="2"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B39" s="2" t="s">
+      <c r="B39" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="4" t="s">
+      <c r="C39" s="3"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="4"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="5" t="s">
         <v>50</v>
       </c>
       <c r="J39" s="2"/>
@@ -2875,19 +2970,19 @@
       <c r="Z39" s="2"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="2" t="s">
+      <c r="A40" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-      <c r="E40" s="2"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="2"/>
-      <c r="I40" s="4" t="s">
+      <c r="C40" s="3"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="5" t="s">
         <v>50</v>
       </c>
       <c r="J40" s="2"/>
@@ -2909,19 +3004,19 @@
       <c r="Z40" s="2"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="2" t="s">
+      <c r="A41" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="B41" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="2"/>
-      <c r="I41" s="4" t="s">
+      <c r="C41" s="3"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3"/>
+      <c r="H41" s="3"/>
+      <c r="I41" s="5" t="s">
         <v>50</v>
       </c>
       <c r="J41" s="2"/>
@@ -2943,19 +3038,19 @@
       <c r="Z41" s="2"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="2" t="s">
+      <c r="A42" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="2"/>
-      <c r="I42" s="4" t="s">
+      <c r="C42" s="3"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+      <c r="H42" s="3"/>
+      <c r="I42" s="5" t="s">
         <v>61</v>
       </c>
       <c r="J42" s="2"/>
@@ -2977,21 +3072,23 @@
       <c r="Z42" s="2"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="2" t="s">
+      <c r="A43" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="5" t="s">
+      <c r="C43" s="3"/>
+      <c r="D43" s="6"/>
+      <c r="E43" s="6">
+        <v>0.818075</v>
+      </c>
+      <c r="F43" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
-      <c r="I43" s="4" t="s">
+      <c r="G43" s="3"/>
+      <c r="H43" s="3"/>
+      <c r="I43" s="5" t="s">
         <v>61</v>
       </c>
       <c r="J43" s="2"/>
@@ -3013,19 +3110,19 @@
       <c r="Z43" s="2"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="2" t="s">
+      <c r="A44" s="3" t="s">
         <v>15</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="4" t="s">
+      <c r="C44" s="3"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="5" t="s">
         <v>61</v>
       </c>
       <c r="J44" s="2"/>
@@ -3047,19 +3144,19 @@
       <c r="Z44" s="2"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="2" t="s">
+      <c r="A45" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="4" t="s">
+      <c r="C45" s="3"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3"/>
+      <c r="H45" s="3"/>
+      <c r="I45" s="5" t="s">
         <v>61</v>
       </c>
       <c r="J45" s="2"/>
@@ -3081,19 +3178,19 @@
       <c r="Z45" s="2"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="2" t="s">
+      <c r="A46" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="4" t="s">
+      <c r="C46" s="3"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
+      <c r="H46" s="3"/>
+      <c r="I46" s="5" t="s">
         <v>61</v>
       </c>
       <c r="J46" s="2"/>
@@ -3115,19 +3212,19 @@
       <c r="Z46" s="2"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="2" t="s">
+      <c r="A47" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
-      <c r="I47" s="4" t="s">
+      <c r="C47" s="3"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+      <c r="H47" s="3"/>
+      <c r="I47" s="5" t="s">
         <v>61</v>
       </c>
       <c r="J47" s="2"/>
@@ -3149,19 +3246,19 @@
       <c r="Z47" s="2"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="2" t="s">
+      <c r="A48" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="4" t="s">
+      <c r="C48" s="3"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="4"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="3"/>
+      <c r="I48" s="5" t="s">
         <v>61</v>
       </c>
       <c r="J48" s="2"/>
@@ -3183,19 +3280,19 @@
       <c r="Z48" s="2"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="2" t="s">
+      <c r="A49" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="4" t="s">
+      <c r="C49" s="3"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="4"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="3"/>
+      <c r="I49" s="5" t="s">
         <v>61</v>
       </c>
       <c r="J49" s="2"/>
@@ -3217,19 +3314,19 @@
       <c r="Z49" s="2"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="2" t="s">
+      <c r="A50" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="2"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-      <c r="I50" s="4" t="s">
+      <c r="C50" s="3"/>
+      <c r="D50" s="4"/>
+      <c r="E50" s="4"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="3"/>
+      <c r="I50" s="5" t="s">
         <v>61</v>
       </c>
       <c r="J50" s="2"/>
@@ -3251,19 +3348,19 @@
       <c r="Z50" s="2"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="2" t="s">
+      <c r="A51" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B51" s="2" t="s">
+      <c r="B51" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
-      <c r="E51" s="2"/>
-      <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
-      <c r="H51" s="2"/>
-      <c r="I51" s="4" t="s">
+      <c r="C51" s="3"/>
+      <c r="D51" s="4"/>
+      <c r="E51" s="4"/>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3"/>
+      <c r="H51" s="3"/>
+      <c r="I51" s="5" t="s">
         <v>61</v>
       </c>
       <c r="J51" s="2"/>
@@ -8824,6 +8921,14 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
+  <dataValidations>
+    <dataValidation type="list" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="I2:I51">
+      <formula1>"Python,Java,C++,Julia,R"</formula1>
+    </dataValidation>
+  </dataValidations>
   <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId3"/>
+  </tableParts>
 </worksheet>
 </file>